--- a/database/AcademicAtlas.xlsx
+++ b/database/AcademicAtlas.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -528,6 +528,1777 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COMP-0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>International Mathematical Olympiad (IMO)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>International Mathematical Olympiad Foundation</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>National team selection required; pre-university students</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Annual international mathematics competition for pre-university students, held since 1959; national teams compete in two exam papers.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.imo-official.org/</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Free (national selection process varies by country)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Team selection is handled by each country's national olympiad committee, not centrally; host country/dates change yearly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>COMP-0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>International Physics Olympiad (IPhO)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>International Physics Olympiad Organization</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>National team selection required; pre-university students</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Annual international physics competition for secondary school students, held since 1967.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.ipho-new.org/</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Free (national selection process varies by country)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Selection handled nationally; host country/dates change yearly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>COMP-0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>International Chemistry Olympiad (IChO)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>International Chemistry Olympiad International Information Centre</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>National team selection required; secondary school students</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Annual international chemistry competition held since 1968, combining theoretical and experimental exams.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.icho-official.org/</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Free (national selection process varies by country)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Selection handled nationally; host country/dates change yearly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>COMP-0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>International Olympiad in Informatics (IOI)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IOI General Assembly</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>National team selection required; pre-university students</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Annual international programming/algorithms competition for secondary school students, held since 1989.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://ioinformatics.org/</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Free (national selection process varies by country)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Selection handled nationally; host country/dates change yearly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>COMP-0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>International Biology Olympiad (IBO)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>International Biology Olympiad e.V.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>National team selection required; pre-university students under 20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Annual international biology competition for secondary school students, held since 1990.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.ibo-info.org/en/</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Free (national selection process varies by country)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Selection handled nationally; host country/dates change yearly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>COMP-0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Regeneron International Science and Engineering Fair (ISEF)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Society for Science</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Must first win at a Society-affiliated local/regional/state/national science fair</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>World's largest international pre-college science competition; finalists qualify through affiliated fairs in 60+ countries, regions, and territories.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.societyforscience.org/isef/</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Free to compete (affiliate fair/travel costs vary)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Entry is via affiliated local fairs, not direct application; affiliate fair deadlines vary by region.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>COMP-0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>John Locke Institute Essay Competition (Global Essay Prize)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>John Locke Institute</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Open globally; no age restriction stated</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Annual essay competition across philosophy, politics, economics, history, psychology, theology, and law; participants from 100+ countries.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.johnlockeinstitute.com/</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Deadline changes annually; check official site for current cycle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>COMP-0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>World Scholar's Cup</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>World Scholar's Cup</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Teams of three students; three age divisions</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Global academic competition combining a quiz bowl, collaborative writing, team debate, and a Tournament of Champions at Yale University; regional rounds in 70+ countries.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.scholarscup.org/</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Regional round dates/fees vary by location; check local round listing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RES-0001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Research programs / opportunities</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Research Science Institute (RSI)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Center for Excellence in Education (CEE), hosted at MIT</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>United States (international students apply via home-country selection)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>US students with one year left before high school graduation (seniors not eligible); international applicants apply through their own country's selection process</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Free 6-week on-campus summer research program combining STEM coursework with mentored research; approximately 100 students selected annually.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.cee.org/programs/research-science-institute</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>International admission runs through separate national selection procedures with their own timelines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RES-0002</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Research programs / opportunities</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PRIMES (Program for Research in Mathematics, Engineering and Science for High School Students)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MIT Department of Mathematics</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>High school sophomores/juniors; specific grades vary by track (MIT PRIMES, PRIMES-USA, PRIMES Circle, Yulia's Dream)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Year-long mentored research program in mathematics, computer science, and computational biology for high school students.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://math.mit.edu/research/highschool/primes/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Multiple tracks with different eligibility/geography; see official site for the specific track.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RES-0003</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Research programs / opportunities</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Simons Summer Research Program</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stony Brook University</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>US citizens/permanent residents; high school juniors, at least 16 by program start, nominated by their school</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>7-week mentored research program pairing approximately 40 selected high school students with Stony Brook University faculty.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.stonybrook.edu/simons/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Requires school nomination (max 2 per school); highly selective (~5% acceptance rate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SUM-0001</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Summer schools</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Summer Science Program (SSP)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SSP International (nonprofit)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>High school juniors</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5-week residential summer research program in astrophysics, biochemistry, bacterial genomics, or synthetic chemistry, held on partner college campuses.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://ssp.org/</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>UNKNOWN (see Fees &amp; Financial Aid page)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Cost varies by track/campus; need-based financial aid available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SUM-0002</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Summer schools</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Yale Young Global Scholars (YYGS)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Yale University</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>High school students from around the world (150+ countries)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Two-week residential summer sessions at Yale across three tracks: Innovations in Science &amp; Technology, Politics of Law &amp; Economics, and Solving Global Challenges.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://globalscholars.yale.edu/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Paid (need-based financial aid and scholarships available)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Tuition varies by session; see site for current pricing and aid options.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SUM-0003</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Summer schools</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MITES (MIT Introduction to Technology, Engineering, and Science)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Massachusetts Institute of Technology</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>United States (MITES Saturdays limited to Boston/Cambridge/Lawrence, MA)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>US citizens/permanent residents, 11th grade, for MITES Summer/Semester; MITES Saturdays limited to Boston-area public school students grades 7-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Free residential (Summer) or remote (Semester) STEM enrichment program at MIT for underrepresented high school students.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://mites.mit.edu/</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Free (students only cover transportation)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Multiple program tracks (Summer/Semester/Saturdays) with different eligibility and formats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SCHOL-0001</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Scholarships</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Davis United World College Scholars Program</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Administered by Middlebury College (founded by Shelby Davis and Phil Geier)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>International (for UWC graduates attending US universities)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Graduates of the 18 United World College (UWC) high schools</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Need-based financial aid for UWC graduates pursuing higher education at 100+ partner colleges/universities in the United States.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.davisuwcscholars.org/</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Need-based (amount varies)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Only open to UWC graduates, not the general public.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SCHOL-0002</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Scholarships</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>QuestBridge National College Match</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>QuestBridge</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>High-achieving high school seniors from low-income backgrounds</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Matches selected students with full four-year scholarships at QuestBridge partner colleges.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.questbridge.org/</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Full four-year scholarship (need-based)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Applicants rank partner colleges; matches are binding at some partners, similar to Early Decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>COURSE-0001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Academic courses</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Center for Talented Youth (CTY)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>United States (online option available internationally)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grades 2-12; qualification via standardized test scores (e.g., 95th+ percentile for Advanced CTY Level)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Academic enrichment courses (in-person and online) for advanced learners, spanning STEM and humanities subjects.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://cty.jhu.edu/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Paid, varies by course (e.g., ~$7,801 for a residential course); need-based financial aid available; $15 application fee</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Tuition varies significantly by course/length; see course catalog for exact pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>COURSE-0002</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Academic courses</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Stanford Online High School</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stanford University (Stanford Pre-Collegiate Studies)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>International (fully online)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Academically advanced students, grades 7-12</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Accredited, fully online private high school with live seminar-style classes; awards approximately $2.5M annually in financial aid.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://onlinehighschool.stanford.edu/</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Paid (financial aid available)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Full diploma-granting school, not a single course; admissions is selective.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>INNOV-0001</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Innovation challenges</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Conrad Challenge</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Conrad Foundation</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ages 13-18, teams of 2-5 students</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Multi-stage innovation/entrepreneurship competition where student teams design solutions to real-world problems, culminating in an in-person Innovation Summit.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.conradchallenge.org/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Free to start (Activation/Lean Canvas stages); $499/team for Innovation Stage; $499/person for in-person Summit; financial aid available</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Costs apply only at later stages; discounts available for Title I schools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>INNOV-0002</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Innovation challenges</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Technovation Girls</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Technovation (nonprofit)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Girls/underrepresented genders in tech, team-based</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Global technology entrepreneurship program where student teams build mobile/AI solutions to community problems.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.technovation.org/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Program registration is managed via technovationchallenge.org; confirm current eligibility there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>JOUR-0001</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Academic journals &amp; publications</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>The Concord Review</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>The Concord Review, Inc.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Secondary school students (history research papers)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Quarterly journal publishing academic history research papers written by secondary school students; also operates the National Writing Board assessment service.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.tcr.org/</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Typical submission is a long-form (~5,000+ word) history research paper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JOUR-0002</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Academic journals &amp; publications</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Journal of Student Research (High School Edition)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Journal of Student Research (Houston, TX)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>First author must be a high school student (grades 9-12) with a listed teacher/advisor</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Peer-reviewed, open-access multidisciplinary journal publishing high school, undergraduate, and graduate student research (AP Research, IB, honors research, etc.).</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.jsr.org/</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Paid Article Processing Charge: $50 at submission + $299 after acceptance</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Double-blind peer review; APC charged in two phases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CONF-0001</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Conferences &amp; academic events</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Harvard Model United Nations (HMUN)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Harvard College (student-run)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>High school students; delegations from 60+ countries</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Large in-person Model UN conference held in Boston, run by Harvard undergraduates, simulating international diplomacy committees.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.harvardmun.org/</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Held annually in late January; check official site for current session dates/fees.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database/AcademicAtlas.xlsx
+++ b/database/AcademicAtlas.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Deadline changes annually; check official site for current cycle.</t>
+          <t>The 2026 cycle is closed (registration by March 31, submission by May 31, 2026). Runs annually; the 2027 cycle typically opens registration in early February with a late-May submission deadline. Free to enter by the regular deadline.</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>International admission runs through separate national selection procedures with their own timelines.</t>
+          <t>Applications typically open in the fall with a mid-December deadline (RSI 2026 was December 10, 2025). RSI 2027 dates are announced by CEE in fall 2026. Highly selective; free to attend.</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Multiple tracks with different eligibility/geography; see official site for the specific track.</t>
+          <t>The application link appears on the MIT PRIMES site in September; the deadline is typically around December 1 (PRIMES 2026 was December 1, 2025). Greater-Boston students for PRIMES; PRIMES-USA is open to U.S. students nationwide.</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Applicants rank partner colleges; matches are binding at some partners, similar to Early Decision.</t>
+          <t>The 2026 National College Match application is due October 1, 2026 (11:59pm PT); match rankings due October 15. QuestBridge also runs the College Prep Scholarship for juniors with a late-March deadline.</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Costs apply only at later stages; discounts available for Title I schools.</t>
+          <t>Runs on an annual season; the 2025-26 season opened August 28, 2025 (activation/registration through October 30) with the Innovation Summit in April 2026. The 2026-27 season is expected to open in late August 2026.</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Typical submission is a long-form (~5,000+ word) history research paper.</t>
+          <t>Fixed quarterly submission deadlines each year: February 1, May 1, August 1, and November 1. The next deadline is August 1, 2026 (Winter issue). Published quarterly.</t>
         </is>
       </c>
     </row>
@@ -2296,6 +2296,1007 @@
       <c r="O24" t="inlineStr">
         <is>
           <t>Held annually in late January; check official site for current session dates/fees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>COMP-0009</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Regeneron Science Talent Search (STS)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Society for Science</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>U.S. high school seniors (and eligible U.S. students studying abroad) submitting original, independent research.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>The oldest and most prestigious pre-college science research competition in the U.S. (founded 1942). Entrants submit original research and a full application for holistic review; about $3.1 million in awards, with a top prize of $250,000.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.societyforscience.org/regeneron-sts/</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>The 2027 application is open June 1 - November 5, 2026 (8pm ET). Top 40 finalists compete in Washington, D.C., in March.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>COMP-0010</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Breakthrough Junior Challenge</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Breakthrough Prize Foundation</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Students aged 13-18 worldwide; individual entry.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Global science-communication competition in which students create an original short video (up to two minutes) explaining a concept in physics, the life sciences, or mathematics. The grand prize includes a $250,000 college scholarship, plus prizes for the student's teacher and school.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://breakthroughjuniorchallenge.org/</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026 entries are due September 15, 2026 (11:59pm PDT); entrants must peer-review at least five other submissions by September 30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>INNOV-0003</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Innovation challenges</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Diamond Challenge</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Horn Entrepreneurship, University of Delaware</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>High school students aged 14-18, in teams of 2-4 with an adult advisor; open to any country.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Global high school entrepreneurship competition in which teams develop an original business or social-venture concept and compete for a prize pool of about $100,000.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://diamondchallenge.org/</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Runs annually; the 2026 cycle ran September 17, 2025 - January 15, 2026 with the summit in late April 2026. The next cycle typically opens in September with a mid-January deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>INNOV-0004</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Innovation challenges</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>GENIUS Olympiad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Terra Science and Education, with Rochester Institute of Technology</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>High school students (grades 9-12) worldwide, submitting projects related to environmental issues.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>International high school project competition focused on environmental issues, spanning science, engineering, art, short film, music, creative writing, robotics, and business categories. Finals are held at Rochester Institute of Technology in New York.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://geniusolympiad.org/</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Runs annually; the 2026 project deadline was March 1, 2026 (extended to March 7) with finals in June 2026 at RIT. Check the official site for 2027 dates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SCHOL-0003</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Scholarships</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Coca-Cola Scholars Program</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Coca-Cola Scholars Foundation</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>U.S. high school seniors graduating in the 2026-2027 school year with a minimum 3.0 GPA; U.S. citizens or eligible status.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Achievement-based scholarship that recognizes 150 U.S. high school seniors each year with a $20,000 college scholarship, selected for leadership, service, and academic excellence.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.coca-colascholarsfoundation.org/apply/</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>$20,000 award</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>The 2027 application is open August 3 - September 30, 2026 (5pm ET). 150 scholars are selected annually.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SCHOL-0004</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Scholarships</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>The Gates Scholarship</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bill &amp; Melinda Gates Foundation</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>U.S. high school seniors from low-income households who are Pell-eligible and members of a minority ethnic group, with a strong academic record.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Highly selective, last-dollar scholarship covering the full cost of attendance not met by other financial aid, for outstanding minority high school seniors from low-income households.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.thegatesscholarship.org/scholarship/</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Full cost of attendance (last-dollar)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>The 2027 application is available July 15 - September 15, 2026. A last-dollar award covering full cost of attendance beyond other aid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SUM-0004</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Summer schools</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PROMYS (Program in Mathematics for Young Scientists)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PROMYS, at Boston University</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Motivated high school students (typically age 15+) with a strong interest in mathematics.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Six-week residential summer program at Boston University immersing students in deep exploration of number theory and creative mathematical problem-solving alongside mentors and researchers.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://promys.org/</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Paid (need-based financial aid available)</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Held each summer at Boston University; the 2026 program ran June 28 - August 8 with a February 27, 2026 application deadline. The 2027 application typically opens in winter with a late-February/early-March deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SUM-0005</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Summer schools</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ross Mathematics Program</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Ross Mathematics Foundation</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Pre-college students (typically age 15+) with a strong interest in mathematics.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Intensive residential summer program (about six weeks) centered on deep exploration of number theory, emphasizing independent and abstract mathematical thinking.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://rossprogram.org/</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Paid (financial aid available)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Held each summer; the 2026 application deadline was around March 8, 2026 (now closed). The 2027 application typically opens in winter with an early-March deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SUM-0006</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Summer schools</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>COSMOS (California State Summer School for Mathematics and Science)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>University of California</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>High school students (grades 8-12) with a strong record in math and science; primarily California residents, with out-of-state applicants accepted at some campuses.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Four-week residential STEM summer program hosted across several University of California campuses, offering intensive clusters in advanced mathematics, science, and engineering.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://cosmos-ucop.ucdavis.edu/</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Paid (financial aid available)</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Hosted at UC campuses including Davis, Irvine, San Diego, and Santa Cruz. The summer 2026 application closed February 6, 2026; the 2027 application typically opens in January with an early-February deadline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>JOUR-0003</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Academic journals &amp; publications</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Journal of Emerging Investigators (JEI)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Journal of Emerging Investigators</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Middle and high school students (grades 6-12), age 13+, of any nationality. Manuscripts must be submitted by an adult mentor or teacher.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Open-access, peer-reviewed journal (founded by Harvard graduate students) that publishes original, hypothesis-driven research by middle and high school students in the life and physical sciences.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://emerginginvestigators.org/</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>$49 submission fee</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Rolling submissions; a single $49 fee covers the full review-and-publication process. As of March 2026, JEI focuses on hypothesis-driven life and experimental physical sciences (no purely computational or dataset-only projects).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>JOUR-0004</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Academic journals &amp; publications</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>National High School Journal of Science (NHSJS)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>National High School Journal of Science</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>High school students (grades 9-12); the primary author must be a high school student.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Free, open-access, peer-reviewed online science journal run for and by high school students, publishing original research papers, reports, and short articles.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://nhsjs.com/</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Rolling submissions with no submission or publication fees.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>RES-0004</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Research programs / opportunities</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Pioneer Academics</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pioneer Academics</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>High school students worldwide (typically age 15+); selective admission.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Accredited online research program that pairs high school students worldwide with university professors for independent research, culminating in a college-credit-bearing research paper.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://pioneeracademics.com/</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Paid (financial aid available)</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Term-based rolling admission; attending an info session unlocks a priority deadline. On average, fewer than a third of applicants are admitted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>COURSE-0003</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Academic courses</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CS50x: Introduction to Computer Science (HarvardX)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Harvard University (HarvardX, on edX)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Open to all; no prerequisites (beginner-friendly).</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Harvard's free introduction to computer science and the art of programming (CS50x), covering C, Python, SQL, JavaScript, HTML/CSS, algorithms, and data structures. Self-paced, with a free audit track.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://cs50.harvard.edu/x/</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Free (optional paid certificate)</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Self-paced with open enrollment via edX; the audit track (lectures and assignments) is free, with an optional paid verified certificate.</t>
         </is>
       </c>
     </row>

--- a/database/AcademicAtlas.xlsx
+++ b/database/AcademicAtlas.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -527,6 +527,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Eligibility_Scope</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -604,6 +609,11 @@
           <t>Team selection is handled by each country's national olympiad committee, not centrally; host country/dates change yearly.</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -681,6 +691,11 @@
           <t>Selection handled nationally; host country/dates change yearly.</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -758,6 +773,11 @@
           <t>Selection handled nationally; host country/dates change yearly.</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -835,6 +855,11 @@
           <t>Selection handled nationally; host country/dates change yearly.</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -912,6 +937,11 @@
           <t>Selection handled nationally; host country/dates change yearly.</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -989,6 +1019,11 @@
           <t>Entry is via affiliated local fairs, not direct application; affiliate fair deadlines vary by region.</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1066,6 +1101,11 @@
           <t>The 2026 cycle is closed (registration by March 31, submission by May 31, 2026). Runs annually; the 2027 cycle typically opens registration in early February with a late-May submission deadline. Free to enter by the regular deadline.</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1143,6 +1183,11 @@
           <t>Regional round dates/fees vary by location; check local round listing.</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1172,7 +1217,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>US students with one year left before high school graduation (seniors not eligible); international applicants apply through their own country's selection process</t>
+          <t>Rising high school seniors aged 16+ by July 1. Open to U.S. citizens/permanent residents and to international students from participating countries (about 30 international places, via national selection).</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1218,6 +1263,11 @@
       <c r="O10" t="inlineStr">
         <is>
           <t>Applications typically open in the fall with a mid-December deadline (RSI 2026 was December 10, 2025). RSI 2027 dates are announced by CEE in fall 2026. Highly selective; free to attend.</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
     </row>
@@ -1297,6 +1347,11 @@
           <t>The application link appears on the MIT PRIMES site in September; the deadline is typically around December 1 (PRIMES 2026 was December 1, 2025). Greater-Boston students for PRIMES; PRIMES-USA is open to U.S. students nationwide.</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>US only</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1366,12 +1421,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
           <t>Requires school nomination (max 2 per school); highly selective (~5% acceptance rate).</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>US only</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1503,17 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>Cost varies by track/campus; need-based financial aid available.</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
     </row>
@@ -1528,6 +1593,11 @@
           <t>Tuition varies by session; see site for current pricing and aid options.</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1597,12 +1667,17 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>Multiple program tracks (Summer/Semester/Saturdays) with different eligibility and formats.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>US only</t>
         </is>
       </c>
     </row>
@@ -1682,6 +1757,11 @@
           <t>Only open to UWC graduates, not the general public.</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1711,7 +1791,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>High-achieving high school seniors from low-income backgrounds</t>
+          <t>High school seniors currently attending high school in the U.S. (U.S. citizens/permanent residents living abroad are also eligible). Students living outside the U.S. are not eligible for the Match.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1757,6 +1837,11 @@
       <c r="O17" t="inlineStr">
         <is>
           <t>The 2026 National College Match application is due October 1, 2026 (11:59pm PT); match rankings due October 15. QuestBridge also runs the College Prep Scholarship for juniors with a late-March deadline.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>US only</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1913,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>Tuition varies significantly by course/length; see course catalog for exact pricing.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
     </row>
@@ -1913,6 +2003,11 @@
           <t>Full diploma-granting school, not a single course; admissions is selective.</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1990,6 +2085,11 @@
           <t>Runs on an annual season; the 2025-26 season opened August 28, 2025 (activation/registration through October 30) with the Innovation Summit in April 2026. The 2026-27 season is expected to open in late August 2026.</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2067,6 +2167,11 @@
           <t>Program registration is managed via technovationchallenge.org; confirm current eligibility there.</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2144,6 +2249,11 @@
           <t>Fixed quarterly submission deadlines each year: February 1, May 1, August 1, and November 1. The next deadline is August 1, 2026 (Winter issue). Published quarterly.</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2221,6 +2331,11 @@
           <t>Double-blind peer review; APC charged in two phases.</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2298,6 +2413,11 @@
           <t>Held annually in late January; check official site for current session dates/fees.</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2375,6 +2495,11 @@
           <t>The 2027 application is open June 1 - November 5, 2026 (8pm ET). Top 40 finalists compete in Washington, D.C., in March.</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>US only</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2452,6 +2577,11 @@
           <t>2026 entries are due September 15, 2026 (11:59pm PDT); entrants must peer-review at least five other submissions by September 30.</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2529,6 +2659,11 @@
           <t>Runs annually; the 2026 cycle ran September 17, 2025 - January 15, 2026 with the summit in late April 2026. The next cycle typically opens in September with a mid-January deadline.</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2606,6 +2741,11 @@
           <t>Runs annually; the 2026 project deadline was March 1, 2026 (extended to March 7) with finals in June 2026 at RIT. Check the official site for 2027 dates.</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2683,6 +2823,11 @@
           <t>The 2027 application is open August 3 - September 30, 2026 (5pm ET). 150 scholars are selected annually.</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>US only</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2760,6 +2905,11 @@
           <t>The 2027 application is available July 15 - September 15, 2026. A last-dollar award covering full cost of attendance beyond other aid.</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>US only</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2837,6 +2987,11 @@
           <t>Held each summer at Boston University; the 2026 program ran June 28 - August 8 with a February 27, 2026 application deadline. The 2027 application typically opens in winter with a late-February/early-March deadline.</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2914,6 +3069,11 @@
           <t>Held each summer; the 2026 application deadline was around March 8, 2026 (now closed). The 2027 application typically opens in winter with an early-March deadline.</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2991,6 +3151,11 @@
           <t>Hosted at UC campuses including Davis, Irvine, San Diego, and Santa Cruz. The summer 2026 application closed February 6, 2026; the 2027 application typically opens in January with an early-February deadline.</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>US only</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3068,6 +3233,11 @@
           <t>Rolling submissions; a single $49 fee covers the full review-and-publication process. As of March 2026, JEI focuses on hypothesis-driven life and experimental physical sciences (no purely computational or dataset-only projects).</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3145,6 +3315,11 @@
           <t>Rolling submissions with no submission or publication fees.</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3222,6 +3397,11 @@
           <t>Term-based rolling admission; attending an info session unlocks a priority deadline. On average, fewer than a third of applicants are admitted.</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3297,6 +3477,749 @@
       <c r="O37" t="inlineStr">
         <is>
           <t>Self-paced with open enrollment via edX; the audit track (lectures and assignments) is free, with an optional paid verified certificate.</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>COMP-0011</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>International Olympiad on Astronomy and Astrophysics (IOAA)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>International Olympiad on Astronomy and Astrophysics</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Secondary-school students selected through their national astronomy/astrophysics olympiad; about 50 countries participate.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Annual international competition in astronomy and astrophysics for secondary-school students, with theoretical, data-analysis, and observational rounds.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://ioaastrophysics.org/</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-09-25 - 2026-10-05 (Hanoi, Vietnam)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Free (national selection varies by country)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Participation is through each country's national olympiad selection; the 19th IOAA is in Hanoi, Vietnam. Turkiye competes via its national astronomy olympiad.</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>COMP-0012</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>International Linguistics Olympiad (IOL)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>International Linguistics Olympiad</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Secondary-school students selected through their national linguistics olympiad; 40+ countries and territories.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>One of the international science olympiads: students solve self-contained linguistic puzzles from a wide range of languages using logic and reasoning, in individual and team contests.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://ioling.org/</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-07-26 - 2026-08-02 (Bucharest, Romania)</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Free (national selection varies by country)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Entry is via national linguistics olympiad selection; the 23rd IOL is in Bucharest, Romania.</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>COMP-0013</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>International Geography Olympiad (iGeo)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>International Geographical Union (IGU) Olympiad Task Force</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Students aged 16-19 selected through their national geography olympiad; about 50 countries.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Annual competition for 16-19-year-old geography students, comprising a written test, a multimedia test, and substantial fieldwork.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://geoolympiad.org/</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026 (Istanbul, Turkiye)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Free (national selection varies by country)</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Entry is via national geography olympiad selection. iGeo 2026 is hosted in Istanbul, Turkiye.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>COMP-0014</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>European Girls' Mathematical Olympiad (EGMO)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>European Girls' Mathematical Olympiad</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Female secondary-school students selected through their national mathematical olympiad; 60+ countries, including many beyond Europe.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Premier international mathematical olympiad for female secondary-school students, with two exam papers held over two days.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.egmo.org/</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Free (national selection varies by country)</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Entry is via each country's national mathematical olympiad selection for female students; 67 countries participated in 2026. Turkiye participates.</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SUM-0007</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Summer schools</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>London International Youth Science Forum (LIYSF)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>London International Youth Science Forum</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Students aged 16-21 with a strong interest in science; open worldwide (80+ countries).</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Two-week residential STEM summer forum in London with lectures by leading scientists, lab visits, and demonstrations, bringing together about 500 students from 80+ countries.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.liysf.org.uk/</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-07-19 - 2026-08-01 (London)</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Paid (GBP 3,295 on-campus; GBP 395 virtual)</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Apply by about 31 May each year (the 2026 deadline was 31 May; program 19 Jul - 1 Aug 2026). On-campus and virtual options available.</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>INNOV-0005</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Innovation challenges</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>FIRST Global Challenge</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>FIRST Global (International FIRST Committee Association)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>High school students (ages ~14-18); one national team per country, selected by the national organization; 190+ countries.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Olympics-style international robotics competition in which one team per nation builds and programs a robot to tackle a global challenge theme.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://first.global/</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-10-07 - 2026-10-10 (Incheon, Republic of Korea)</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Participation is via each country's national FIRST Global team. The 2026 event is in Incheon, Korea (theme: Igniting Innovation).</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CONF-0002</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Conferences &amp; academic events</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>The Hague International Model United Nations (THIMUN)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>THIMUN Foundation</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Secondary-school students in registered school delegations; students from 100+ countries.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>One of the world's largest and most international Model UN conferences: a four-day simulation of the UN for secondary-school students, held annually in The Hague.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://thehague.thimun.org/</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>UNKNOWN (late January each year, The Hague)</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Schools register delegations; about 3,200 participants from ~200 schools across 100+ countries. Held at the end of January in The Hague.</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CONF-0003</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Conferences &amp; academic events</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Yale Model United Nations (YMUN)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Yale International Relations Association (YIRA)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>High school students worldwide, individually or in school delegations; about 40 countries represented.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Four-day international-relations simulation for high school students held on Yale's campus in New Haven, one of the largest high school Model UN conferences.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://ymun.org/</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>UNKNOWN (January each year, New Haven)</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Held each January at Yale; 1,800+ delegates from 40+ countries. YIRA also runs YMUN conferences abroad (Korea, Dubai, Taiwan, Europe, Singapore).</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SCHOL-0005</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Scholarships</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Rise (Rise for the World)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Schmidt Futures &amp; the Rhodes Trust</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Young people aged 15-17 working in service of others; open to applicants worldwide.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Global program that selects promising 15-17-year-olds and supports them for life with need-based scholarships, mentorship, funding, and career development.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.risefortheworld.org/</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Free (need-based scholarships and funding provided)</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Applications run on an annual cycle (historically opening in the fall/winter). 100 Global Winners are selected each year and receive lifelong benefits. Open worldwide.</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
     </row>

--- a/database/AcademicAtlas.xlsx
+++ b/database/AcademicAtlas.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -532,6 +532,11 @@
           <t>Eligibility_Scope</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Qualifies_For</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4220,6 +4225,702 @@
       <c r="P46" t="inlineStr">
         <is>
           <t>International</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>COMP-0015</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TÜBİTAK National Mathematics Olympiad (Ulusal Matematik Olimpiyatı)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TÜBİTAK (Scientific and Technological Research Council of Türkiye) — BİDEB</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Students enrolled at schools in Türkiye (roughly grades 9-11 for the high-school branches; final-year students are generally excluded from the international-team track).</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Türkiye's national mathematics olympiad, run by TÜBİTAK as a two-stage exam: a multiple-choice first stage held across all 81 provinces (and the TRNC), then a written/practical second stage. Top performers train at national team camps and are selected for Türkiye's team to the International Mathematical Olympiad (IMO).</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://bilimolimpiyatlari.tubitak.gov.tr/tr/ulusal-bilim-olimpiyatlari</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-05-16 (first-stage exam; annual)</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Part of the TÜBİTAK Science Olympiads (TÜBİTAK 2202, run by BİDEB). The 2026 first-stage exam was held on 16 May 2026; application dates are announced each year through ebideb.tubitak.gov.tr.</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Türkiye only</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>COMP-0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>COMP-0016</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TÜBİTAK National Physics Olympiad (Ulusal Fizik Olimpiyatı)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TÜBİTAK (Scientific and Technological Research Council of Türkiye) — BİDEB</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Students enrolled at schools in Türkiye (roughly grades 9-11 for the high-school branches; final-year students are generally excluded from the international-team track).</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Türkiye's national physics olympiad, run by TÜBİTAK as a two-stage exam: a multiple-choice first stage held across all 81 provinces (and the TRNC), then a written/practical second stage. Top performers train at national team camps and are selected for Türkiye's team to the International Physics Olympiad (IPhO).</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://bilimolimpiyatlari.tubitak.gov.tr/tr/ulusal-bilim-olimpiyatlari</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-05-16 (first-stage exam; annual)</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Part of the TÜBİTAK Science Olympiads (TÜBİTAK 2202, run by BİDEB). The 2026 first-stage exam was held on 16 May 2026; application dates are announced each year through ebideb.tubitak.gov.tr.</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Türkiye only</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>COMP-0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>COMP-0017</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TÜBİTAK National Chemistry Olympiad (Ulusal Kimya Olimpiyatı)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TÜBİTAK (Scientific and Technological Research Council of Türkiye) — BİDEB</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Students enrolled at schools in Türkiye (roughly grades 9-11 for the high-school branches; final-year students are generally excluded from the international-team track).</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Türkiye's national chemistry olympiad, run by TÜBİTAK as a two-stage exam: a multiple-choice first stage held across all 81 provinces (and the TRNC), then a written/practical second stage. Top performers train at national team camps and are selected for Türkiye's team to the International Chemistry Olympiad (IChO).</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://bilimolimpiyatlari.tubitak.gov.tr/tr/ulusal-bilim-olimpiyatlari</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-05-16 (first-stage exam; annual)</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Part of the TÜBİTAK Science Olympiads (TÜBİTAK 2202, run by BİDEB). The 2026 first-stage exam was held on 16 May 2026; application dates are announced each year through ebideb.tubitak.gov.tr.</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Türkiye only</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>COMP-0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>COMP-0018</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TÜBİTAK National Informatics Olympiad (Ulusal Bilgisayar Olimpiyatı)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TÜBİTAK (Scientific and Technological Research Council of Türkiye) — BİDEB</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Students enrolled at schools in Türkiye (roughly grades 9-11 for the high-school branches; final-year students are generally excluded from the international-team track).</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Türkiye's national informatics/computing olympiad, run by TÜBİTAK as a two-stage exam: a multiple-choice first stage held across all 81 provinces (and the TRNC), then a written/practical second stage. Top performers train at national team camps and are selected for Türkiye's team to the International Olympiad in Informatics (IOI).</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://bilimolimpiyatlari.tubitak.gov.tr/tr/ulusal-bilim-olimpiyatlari</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-05-16 (first-stage exam; annual)</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Part of the TÜBİTAK Science Olympiads (TÜBİTAK 2202, run by BİDEB). The 2026 first-stage exam was held on 16 May 2026; application dates are announced each year through ebideb.tubitak.gov.tr.</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Türkiye only</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>COMP-0004</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>COMP-0019</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TÜBİTAK National Biology Olympiad (Ulusal Biyoloji Olimpiyatı)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TÜBİTAK (Scientific and Technological Research Council of Türkiye) — BİDEB</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Students enrolled at schools in Türkiye (roughly grades 9-11 for the high-school branches; final-year students are generally excluded from the international-team track).</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Türkiye's national biology olympiad, run by TÜBİTAK as a two-stage exam: a multiple-choice first stage held across all 81 provinces (and the TRNC), then a written/practical second stage. Top performers train at national team camps and are selected for Türkiye's team to the International Biology Olympiad (IBO).</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://bilimolimpiyatlari.tubitak.gov.tr/tr/ulusal-bilim-olimpiyatlari</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-05-16 (first-stage exam; annual)</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Part of the TÜBİTAK Science Olympiads (TÜBİTAK 2202, run by BİDEB). The 2026 first-stage exam was held on 16 May 2026; application dates are announced each year through ebideb.tubitak.gov.tr.</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Türkiye only</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>COMP-0005</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>COMP-0020</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Türkiye Astronomy and Astrophysics Olympiad (TROAA)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TÜBİTAK — Türkiye Astronomy and Astrophysics Olympiads (TROAA)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Students at schools in Türkiye who are high-school students (or graduate in the competition year) and under 20 as of 1 July of the competition year.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Türkiye's national astronomy and astrophysics olympiad. Candidates are ranked on theoretical, data-analysis and observational performance; the top five form the national team (with a reserve) and attend team camps before the international final.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://olimpiyat.astronomi.org/</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-05-16 (first-stage exam; annual)</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Run within the TÜBİTAK Science Olympiads (astronomy-astrophysics branch); TROAA coordinates the selection and team camps for the International Olympiad on Astronomy and Astrophysics (IOAA). Application dates are announced annually.</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Türkiye only</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>COMP-0011</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>COMP-0021</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TÜBİTAK National Geography Olympiad (Ulusal Coğrafya Olimpiyatı)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TÜBİTAK (Scientific and Technological Research Council of Türkiye) — BİDEB</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Students enrolled at schools in Türkiye (roughly grades 9-11 for the high-school branches; final-year students are generally excluded from the international-team track).</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Türkiye's national geography olympiad, run by TÜBİTAK as a two-stage exam: a multiple-choice first stage held across all 81 provinces (and the TRNC), then a written/practical second stage. Top performers train at national team camps and are selected for Türkiye's team to the International Geography Olympiad (iGeo).</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://bilimolimpiyatlari.tubitak.gov.tr/tr/ulusal-bilim-olimpiyatlari</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-05-16 (first-stage exam; annual)</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Part of the TÜBİTAK Science Olympiads (TÜBİTAK 2202, run by BİDEB). The 2026 first-stage exam was held on 16 May 2026; application dates are announced each year through ebideb.tubitak.gov.tr. Türkiye's iGeo team is selected through national geography selection, coordinated with the Turkish Geographical Society (Türk Coğrafya Kurumu, TCK), an IGU member.</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Türkiye only</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>COMP-0013</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>COMP-0022</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>International competitions</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TÜBİTAK 2204-A High School Students Research Projects Competition (Lise Öğrencileri Araştırma Projeleri Yarışması)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TÜBİTAK (Scientific and Technological Research Council of Türkiye)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>High-school students at schools in Türkiye, entering an original research project (individually or in pairs, with an advisor).</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Türkiye's national high-school research-project competition, judged through regional and final stages across many subject areas. The strongest projects are selected to represent Türkiye at the Regeneron International Science and Engineering Fair (ISEF).</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://tubitak.gov.tr/en/competitions/2204-high-school-students-research-projects-competition</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Türkiye's ISEF-affiliated fair. Projects advance through preliminary/regional and final evaluations; top projects are chosen to compete at ISEF. Application timing is announced annually by TÜBİTAK.</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Türkiye only</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>COMP-0006</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4349,6 +5050,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -4382,6 +5084,30 @@
       <c r="B13" t="inlineStr">
         <is>
           <t>Valid only for Application_Deadline</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Türkiye only</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Eligibility_Scope value: limited to students in Türkiye (e.g. national olympiads / qualifying stages).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Qualifies_For</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Optional column: ID of the international opportunity a national/regional stage feeds into.</t>
         </is>
       </c>
     </row>

--- a/database/AcademicAtlas.xlsx
+++ b/database/AcademicAtlas.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -537,6 +537,16 @@
           <t>Qualifies_For</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Typical_Window</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -619,6 +629,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -701,6 +716,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +803,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -865,6 +890,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -947,6 +977,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1029,6 +1064,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1111,6 +1151,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Writing; Social Sciences &amp; Humanities; Economics &amp; Business</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1193,6 +1238,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1275,6 +1325,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1357,6 +1412,11 @@
           <t>US only</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Mathematics; Computer Science</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1439,6 +1499,11 @@
           <t>US only</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1521,6 +1586,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Earth &amp; Space; Biology; Chemistry</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1603,6 +1673,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1685,6 +1760,11 @@
           <t>US only</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Robotics; Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1767,6 +1847,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1849,6 +1934,11 @@
           <t>US only</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1931,6 +2021,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2013,6 +2108,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2095,6 +2195,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Robotics; Economics &amp; Business</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2177,6 +2282,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Computer Science; Economics &amp; Business</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2259,6 +2369,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Social Sciences &amp; Humanities; Writing</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2341,6 +2456,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2423,6 +2543,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Social Sciences &amp; Humanities</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2505,6 +2630,11 @@
           <t>US only</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2587,6 +2717,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2669,6 +2804,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Economics &amp; Business</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2751,6 +2891,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Environment; Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2833,6 +2978,11 @@
           <t>US only</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2915,6 +3065,11 @@
           <t>US only</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2997,6 +3152,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3079,6 +3239,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3161,6 +3326,11 @@
           <t>US only</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3243,6 +3413,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3325,6 +3500,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3407,6 +3587,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3489,6 +3674,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3571,6 +3761,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Earth &amp; Space; Physics</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3653,6 +3848,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Linguistics</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3735,6 +3935,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Earth &amp; Space; Social Sciences &amp; Humanities</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3817,6 +4022,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3899,6 +4109,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3981,6 +4196,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Robotics</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4063,6 +4283,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Social Sciences &amp; Humanities</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4145,6 +4370,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Social Sciences &amp; Humanities</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4227,6 +4457,11 @@
           <t>International</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4314,6 +4549,11 @@
           <t>COMP-0001</t>
         </is>
       </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4401,6 +4641,11 @@
           <t>COMP-0002</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4488,6 +4733,11 @@
           <t>COMP-0003</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4575,6 +4825,11 @@
           <t>COMP-0004</t>
         </is>
       </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4662,6 +4917,11 @@
           <t>COMP-0005</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4749,6 +5009,11 @@
           <t>COMP-0011</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Earth &amp; Space; Physics</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4836,6 +5101,11 @@
           <t>COMP-0013</t>
         </is>
       </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Earth &amp; Space; Social Sciences &amp; Humanities</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4921,6 +5191,11 @@
       <c r="Q54" t="inlineStr">
         <is>
           <t>COMP-0006</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
         </is>
       </c>
     </row>
@@ -4935,7 +5210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5050,7 +5325,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -5108,6 +5382,198 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>Optional column: ID of the international opportunity a national/regional stage feeds into.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Subjects</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Covers (Subject column; ';'-separated for multiple)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mathematics</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pure and applied mathematics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Physics</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Physics and astrophysics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Chemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Biology and the life sciences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Programming, informatics, algorithms, AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Robotics</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Engineering, robotics, hardware design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Earth &amp; Space</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Astronomy, geography, geology, earth sciences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Environmental science and sustainability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Economics &amp; Business</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Economics, finance, entrepreneurship.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Social Sciences &amp; Humanities</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>History, philosophy, psychology, social sciences.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Linguistics</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Language and linguistics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Essay, journalism, creative and academic writing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Arts &amp; Design</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Visual, performing, and design disciplines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Medicine &amp; Health</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Medicine, public health, biomedical topics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Spans multiple fields, or a general program.</t>
         </is>
       </c>
     </row>

--- a/database/AcademicAtlas.xlsx
+++ b/database/AcademicAtlas.xlsx
@@ -1138,7 +1138,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1154,6 +1154,11 @@
       <c r="R8" t="inlineStr">
         <is>
           <t>Writing; Social Sciences &amp; Humanities; Economics &amp; Business</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Late May</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1926,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2356,7 +2361,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2617,7 +2622,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2704,7 +2709,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2878,7 +2883,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2894,6 +2899,11 @@
       <c r="R28" t="inlineStr">
         <is>
           <t>Environment; Interdisciplinary</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Early March</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2975,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3052,7 +3062,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3313,7 +3323,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3329,6 +3339,11 @@
       <c r="R33" t="inlineStr">
         <is>
           <t>Interdisciplinary</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>February</t>
         </is>
       </c>
     </row>

--- a/database/AcademicAtlas.xlsx
+++ b/database/AcademicAtlas.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:S61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5214,6 +5214,613 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>RES-0005</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Research programs / opportunities</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Polygence</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Polygence</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>High school students (typically age 13+); open to students worldwide.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>An online research program that pairs high school students one-on-one with expert mentors to design and complete an independent research project or creative output.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.polygence.org/</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Rolling admissions with periodic cohort start dates; financial aid/scholarships available. Confirm current fees and deadlines on the official site.</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>RES-0006</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Research programs / opportunities</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Lumiere Research Scholar Program</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Lumiere Education</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>High school students worldwide (a separate Junior Explorer Program serves grades 6-8).</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>A selective online program in which high school students work one-on-one with PhD mentors to produce an independent research paper.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.lumiere-education.com/</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Runs in seasonal cohorts (e.g. summer, fall, winter, spring) with per-cohort deadlines; financial aid available for low-income students.</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>RES-0007</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Research programs / opportunities</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Horizon Academic Research Program</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Horizon Academic</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>High school students worldwide (typically age 15+); selective admission.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>A selective online program where high school students conduct university-level research in STEM, the social sciences, or the humanities with professor-led seminars or PhD mentorship, culminating in a publishable paper.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.horizoninspires.com/</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Rolling</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Seasonal cohorts (e.g. summer) plus a year-round one-on-one PhD Labs track. Confirm current fees and cohort deadlines on the official site.</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Interdisciplinary</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CONF-0004</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Conferences &amp; academic events</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Berkeley Model United Nations (BMUN)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Model United Nations at UC Berkeley (student-run)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>High school students; delegations from around the world.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>A large, long-running Model UN conference run by UC Berkeley students, where high school delegates debate global issues across a wide range of committees.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://bmun.org/</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2027-03-05 to 2027-03-07</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Held annually at UC Berkeley (the 75th session, BMUN LXXV, is March 5-7, 2027). Delegate fees apply; register as a school delegation. Confirm fees and deadlines on the official site.</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Social Sciences &amp; Humanities</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CONF-0005</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Conferences &amp; academic events</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>National High School Model United Nations (NHSMUN)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>IMUNA (International Model United Nations Association)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Secondary-school students; delegations from around the world.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>A large, long-established Model UN conference for secondary-school students, held in New York City with sessions connected to the United Nations.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://imuna.org/nhsmun/nyc/</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2027-03-12 to 2027-03-20</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Held in NYC each March in two sessions (Session I March 12-15 and Session II March 17-20, 2027). A participant fee applies; register as a school delegation. Confirm fees and deadlines on the official site.</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Social Sciences &amp; Humanities</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>INNOV-0006</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Innovation challenges</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>TEKNOFEST Aerospace and Technology Festival</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Turkish Technology Team Foundation (T3) and the Ministry of Industry and Technology</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Secondary-school and university students, in teams; international teams are accepted in many competition categories.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>A large aerospace and technology festival that runs dozens of student technology competitions - in areas such as robotics, AI, aerospace, and biotechnology - through design and prototype challenges.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://teknofest.org/en/</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Held annually in Türkiye; each of its many sub-competitions announces its own registration timeline. Confirm each competition's eligibility, entry fee (if any), and dates on the official competition guide.</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Robotics; Interdisciplinary</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>COURSE-0004</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Academic courses</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DENEYAP Technology Workshops (Deneyap Teknoloji Atolyeleri)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Turkish Technology Team Foundation (T3), Ministry of Industry and Technology, and TUBITAK</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Students in Türkiye selected from 4th, 5th, 8th and 9th grades and high-school prep classes, residing in provinces open for applications.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>A free, multi-year technology education program that trains selected students in Türkiye across fields such as robotics and coding, artificial intelligence, cyber security, and aerospace technologies.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.deneyap.org/en/</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>A 36-month program (24 months of project-based courses plus 12 months of team work) delivered at DENEYAP workshops across Türkiye. Admission is by an annual selection process (e-exam, then online training/tasks, then a practical exam). Confirm current application dates on the official site.</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Türkiye only</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Engineering &amp; Robotics; Computer Science</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
